--- a/Lyceum_16abril2026/mujerers_en_Lyceum.xlsx
+++ b/Lyceum_16abril2026/mujerers_en_Lyceum.xlsx
@@ -8,13 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd291838b10efa6/Documentos/GitHub/CMMBML_Sobremesas_Modradas/Lyceum_16abril2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{1D3292D4-3D8F-4ED8-BC40-B7F46D946564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66528865-524F-40C6-99DA-780897259A18}"/>
+  <xr:revisionPtr revIDLastSave="197" documentId="8_{1D3292D4-3D8F-4ED8-BC40-B7F46D946564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4418DC1-84A6-40F7-9202-D255B840E3DB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{520C1729-7439-40B7-A682-5E6452D54222}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{520C1729-7439-40B7-A682-5E6452D54222}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="borrador" sheetId="1" r:id="rId1"/>
+    <sheet name="Juego " sheetId="3" r:id="rId2"/>
+    <sheet name="Soluciones" sheetId="2" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Juego '!$A$1:$O$12</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="71">
   <si>
     <r>
       <t xml:space="preserve">                                                           </t>
@@ -1107,13 +1112,150 @@
   </si>
   <si>
     <t>Escritora, etnologa</t>
+  </si>
+  <si>
+    <t>Destacó principalmente en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notas </t>
+  </si>
+  <si>
+    <t>Nombre y enlace</t>
+  </si>
+  <si>
+    <t>Nombres y enlaces</t>
+  </si>
+  <si>
+    <t>PEDAGOGA</t>
+  </si>
+  <si>
+    <t>ETNOLOGA</t>
+  </si>
+  <si>
+    <t>Clara Campoamor</t>
+  </si>
+  <si>
+    <t>abogada, escritora, política</t>
+  </si>
+  <si>
+    <t>ABOGADA</t>
+  </si>
+  <si>
+    <t>POLITICA</t>
+  </si>
+  <si>
+    <t>Zenobia Camprubí</t>
+  </si>
+  <si>
+    <t>escritora, traductora y lingüista</t>
+  </si>
+  <si>
+    <t>TRADUCTORA</t>
+  </si>
+  <si>
+    <t>LINGÜISTA</t>
+  </si>
+  <si>
+    <t>Elena Fortún</t>
+  </si>
+  <si>
+    <t>escritora, literatura infantil</t>
+  </si>
+  <si>
+    <t>Maruja Mallo</t>
+  </si>
+  <si>
+    <t>pintora surrealista</t>
+  </si>
+  <si>
+    <t>PINTORA</t>
+  </si>
+  <si>
+    <t>Nieves González Barrio</t>
+  </si>
+  <si>
+    <t>MEDICA PEDIATRA</t>
+  </si>
+  <si>
+    <t>MEDICA</t>
+  </si>
+  <si>
+    <t>Rosa Spottorno</t>
+  </si>
+  <si>
+    <t>Aciertos</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ernestina de Champourcín</t>
+  </si>
+  <si>
+    <t>Poeta</t>
+  </si>
+  <si>
+    <t>ESCRITORA - POETA</t>
+  </si>
+  <si>
+    <t>Ernestina de Champourcín</t>
+  </si>
+  <si>
+    <t>Victoria Kent</t>
+  </si>
+  <si>
+    <r>
+      <t>abogada</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> y </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>política</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>republicana</t>
+    </r>
+  </si>
+  <si>
+    <t>escritora, crítica de arte y política </t>
+  </si>
+  <si>
+    <t>Margarita Nelken</t>
+  </si>
+  <si>
+    <t>CRITICA ARTE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1141,20 +1283,129 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="14"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF202122"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF233566"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF3366CC"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -1163,7 +1414,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="15"/>
@@ -1177,7 +1428,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1196,6 +1476,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1538,7 +1822,6 @@
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="2"/>
       <c r="C4" s="4"/>
-      <c r="D4" s="5"/>
       <c r="J4" s="3" t="s">
         <v>36</v>
       </c>
@@ -1718,4 +2001,395 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3400AFDC-B441-469B-8F9B-D2DCC4FD6173}">
+  <dimension ref="A2:O12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.5703125" customWidth="1"/>
+    <col min="4" max="11" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6" customWidth="1"/>
+    <col min="13" max="13" width="5.42578125" customWidth="1"/>
+    <col min="14" max="14" width="6" customWidth="1"/>
+    <col min="15" max="15" width="6.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:15" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="M2" s="7"/>
+    </row>
+    <row r="3" spans="1:15" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="18"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+    </row>
+    <row r="4" spans="1:15" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="18"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+    </row>
+    <row r="5" spans="1:15" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="18"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+    </row>
+    <row r="6" spans="1:15" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+    </row>
+    <row r="7" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="18"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+    </row>
+    <row r="8" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="18"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+    </row>
+    <row r="9" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+    </row>
+    <row r="10" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+    </row>
+    <row r="11" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A11" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+    </row>
+    <row r="12" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="18"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{CA7C0ED5-E5C5-44D5-99A3-6ADEC0F86EBD}"/>
+    <hyperlink ref="A4" r:id="rId2" xr:uid="{225CDAE6-7F13-4DB1-82E8-003BF107C4B2}"/>
+    <hyperlink ref="A5" r:id="rId3" xr:uid="{A91805F8-9D81-48D4-A681-AE6D78BD0F56}"/>
+    <hyperlink ref="A6" r:id="rId4" xr:uid="{AF2336AB-A8DF-48C3-A1FD-4874A08E195E}"/>
+    <hyperlink ref="A7" r:id="rId5" xr:uid="{E915C835-AA57-4998-B7D5-1000D168519B}"/>
+    <hyperlink ref="A8" r:id="rId6" xr:uid="{3397EC2A-9C55-4813-BF9C-99D6BF02C944}"/>
+    <hyperlink ref="A9" r:id="rId7" xr:uid="{29340F01-66BF-45C5-8BDF-6F1A9DCA21F8}"/>
+    <hyperlink ref="A10" r:id="rId8" display=" Ernestina de Champourcín" xr:uid="{3CD95760-6D54-494C-BD0B-1882CAC81613}"/>
+    <hyperlink ref="A11" r:id="rId9" xr:uid="{BAEA3720-31E6-4E7F-ADF6-5AF643F88282}"/>
+    <hyperlink ref="A12" r:id="rId10" xr:uid="{486BDCFA-ED45-4A70-80E0-0BA6AC8342AA}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="95" orientation="landscape" horizontalDpi="0" verticalDpi="0" copies="2" r:id="rId11"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3352D7AE-DE03-4C47-9317-E12938A32132}">
+  <dimension ref="A2:C14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="2" max="3" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" xr:uid="{BB636B07-B6D0-43D7-AFED-CBF7587F2CEE}"/>
+    <hyperlink ref="A5" r:id="rId2" xr:uid="{256828DD-6D9C-4D7C-9EEB-23A5F7B410A7}"/>
+    <hyperlink ref="A6" r:id="rId3" xr:uid="{B59B036F-CC4D-43BD-83A9-F8533D865888}"/>
+    <hyperlink ref="A7" r:id="rId4" xr:uid="{21D3DC70-BCDE-4A02-8704-1B7913AA98DB}"/>
+    <hyperlink ref="A8" r:id="rId5" xr:uid="{205F32B7-57F9-4696-8A3D-49E407397A45}"/>
+    <hyperlink ref="A9" r:id="rId6" xr:uid="{F9F8625F-FEDF-42A2-A00D-E1A5BB1F799D}"/>
+    <hyperlink ref="A10" r:id="rId7" xr:uid="{5EE62DE8-8827-4771-A841-7746366596DB}"/>
+    <hyperlink ref="A11" r:id="rId8" xr:uid="{DC517F50-E87F-4206-AE46-36C0CF1CB9C2}"/>
+    <hyperlink ref="A12" r:id="rId9" xr:uid="{285EE5E9-2761-4120-81A5-9DA2575FC0FF}"/>
+    <hyperlink ref="A13" r:id="rId10" xr:uid="{65BFBE20-476C-4C7B-96E6-4201DE5E0E58}"/>
+    <hyperlink ref="A14" r:id="rId11" xr:uid="{E5CB29E8-589A-4CBB-BA7E-DB019D65631F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Lyceum_16abril2026/mujerers_en_Lyceum.xlsx
+++ b/Lyceum_16abril2026/mujerers_en_Lyceum.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="533" documentId="8_{1D3292D4-3D8F-4ED8-BC40-B7F46D946564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECD66C20-74DC-47CA-86D0-4ADC9982573A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{520C1729-7439-40B7-A682-5E6452D54222}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{520C1729-7439-40B7-A682-5E6452D54222}"/>
   </bookViews>
   <sheets>
     <sheet name="Juego " sheetId="3" r:id="rId1"/>
@@ -622,7 +622,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -696,18 +696,11 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -726,6 +719,12 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1071,39 +1070,39 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.453125" customWidth="1"/>
-    <col min="2" max="2" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="17" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.453125" customWidth="1"/>
+    <col min="1" max="1" width="36.42578125" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="17" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-    </row>
-    <row r="2" spans="1:20" ht="162.5" x14ac:dyDescent="0.35">
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="57"/>
+      <c r="P1" s="57"/>
+      <c r="Q1" s="57"/>
+      <c r="R1" s="57"/>
+      <c r="S1" s="57"/>
+      <c r="T1" s="57"/>
+    </row>
+    <row r="2" spans="1:20" ht="165" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1159,8 +1158,8 @@
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:20" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="50" t="s">
+    <row r="3" spans="1:20" ht="24" x14ac:dyDescent="0.25">
+      <c r="A3" s="47" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6"/>
@@ -1180,8 +1179,8 @@
       <c r="P3" s="20"/>
       <c r="Q3" s="3"/>
     </row>
-    <row r="4" spans="1:20" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="50" t="s">
+    <row r="4" spans="1:20" ht="24" x14ac:dyDescent="0.25">
+      <c r="A4" s="47" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="6"/>
@@ -1201,8 +1200,8 @@
       <c r="P4" s="20"/>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5" spans="1:20" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="50" t="s">
+    <row r="5" spans="1:20" ht="24" x14ac:dyDescent="0.25">
+      <c r="A5" s="47" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="6"/>
@@ -1222,8 +1221,8 @@
       <c r="P5" s="20"/>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6" spans="1:20" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="51" t="s">
+    <row r="6" spans="1:20" ht="24" x14ac:dyDescent="0.25">
+      <c r="A6" s="48" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="7"/>
@@ -1243,8 +1242,8 @@
       <c r="P6" s="20"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="1:20" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="45" t="s">
+    <row r="7" spans="1:20" ht="24" x14ac:dyDescent="0.4">
+      <c r="A7" s="43" t="s">
         <v>20</v>
       </c>
       <c r="B7" s="6"/>
@@ -1264,8 +1263,8 @@
       <c r="P7" s="20"/>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8" spans="1:20" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="45" t="s">
+    <row r="8" spans="1:20" ht="24" x14ac:dyDescent="0.4">
+      <c r="A8" s="43" t="s">
         <v>23</v>
       </c>
       <c r="B8" s="6"/>
@@ -1285,8 +1284,8 @@
       <c r="P8" s="20"/>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9" spans="1:20" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="45" t="s">
+    <row r="9" spans="1:20" ht="24" x14ac:dyDescent="0.4">
+      <c r="A9" s="43" t="s">
         <v>26</v>
       </c>
       <c r="B9" s="6"/>
@@ -1306,8 +1305,8 @@
       <c r="P9" s="20"/>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10" spans="1:20" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="45" t="s">
+    <row r="10" spans="1:20" ht="24" x14ac:dyDescent="0.4">
+      <c r="A10" s="43" t="s">
         <v>31</v>
       </c>
       <c r="B10" s="6"/>
@@ -1327,8 +1326,8 @@
       <c r="P10" s="20"/>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11" spans="1:20" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="45" t="s">
+    <row r="11" spans="1:20" ht="24" x14ac:dyDescent="0.4">
+      <c r="A11" s="43" t="s">
         <v>32</v>
       </c>
       <c r="B11" s="6"/>
@@ -1348,8 +1347,8 @@
       <c r="P11" s="20"/>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12" spans="1:20" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="45" t="s">
+    <row r="12" spans="1:20" ht="24" x14ac:dyDescent="0.4">
+      <c r="A12" s="43" t="s">
         <v>34</v>
       </c>
       <c r="B12" s="6"/>
@@ -1369,8 +1368,8 @@
       <c r="P12" s="20"/>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13" spans="1:20" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="45" t="s">
+    <row r="13" spans="1:20" ht="24" x14ac:dyDescent="0.4">
+      <c r="A13" s="43" t="s">
         <v>35</v>
       </c>
       <c r="B13" s="6"/>
@@ -1390,8 +1389,8 @@
       <c r="P13" s="20"/>
       <c r="Q13" s="2"/>
     </row>
-    <row r="14" spans="1:20" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="45" t="s">
+    <row r="14" spans="1:20" ht="24" x14ac:dyDescent="0.4">
+      <c r="A14" s="43" t="s">
         <v>65</v>
       </c>
       <c r="B14" s="6"/>
@@ -1411,8 +1410,8 @@
       <c r="P14" s="20"/>
       <c r="Q14" s="2"/>
     </row>
-    <row r="15" spans="1:20" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="45" t="s">
+    <row r="15" spans="1:20" ht="24" x14ac:dyDescent="0.4">
+      <c r="A15" s="43" t="s">
         <v>40</v>
       </c>
       <c r="B15" s="6"/>
@@ -1432,8 +1431,8 @@
       <c r="P15" s="20"/>
       <c r="Q15" s="2"/>
     </row>
-    <row r="16" spans="1:20" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="45" t="s">
+    <row r="16" spans="1:20" ht="24" x14ac:dyDescent="0.4">
+      <c r="A16" s="43" t="s">
         <v>50</v>
       </c>
       <c r="B16" s="6"/>
@@ -1453,8 +1452,8 @@
       <c r="P16" s="20"/>
       <c r="Q16" s="2"/>
     </row>
-    <row r="17" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="45" t="s">
+    <row r="17" spans="1:17" ht="24" x14ac:dyDescent="0.4">
+      <c r="A17" s="43" t="s">
         <v>48</v>
       </c>
       <c r="B17" s="6"/>
@@ -1474,8 +1473,8 @@
       <c r="P17" s="20"/>
       <c r="Q17" s="2"/>
     </row>
-    <row r="18" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="45" t="s">
+    <row r="18" spans="1:17" ht="24" x14ac:dyDescent="0.4">
+      <c r="A18" s="43" t="s">
         <v>51</v>
       </c>
       <c r="B18" s="6"/>
@@ -1495,8 +1494,8 @@
       <c r="P18" s="20"/>
       <c r="Q18" s="2"/>
     </row>
-    <row r="19" spans="1:17" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="52" t="s">
+    <row r="19" spans="1:17" ht="24" x14ac:dyDescent="0.25">
+      <c r="A19" s="49" t="s">
         <v>53</v>
       </c>
       <c r="B19" s="6"/>
@@ -1516,8 +1515,8 @@
       <c r="P19" s="20"/>
       <c r="Q19" s="2"/>
     </row>
-    <row r="20" spans="1:17" ht="47" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="53" t="s">
+    <row r="20" spans="1:17" ht="48" x14ac:dyDescent="0.4">
+      <c r="A20" s="50" t="s">
         <v>62</v>
       </c>
       <c r="B20" s="6"/>
@@ -1537,8 +1536,8 @@
       <c r="P20" s="20"/>
       <c r="Q20" s="2"/>
     </row>
-    <row r="21" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="45" t="s">
+    <row r="21" spans="1:17" ht="24" x14ac:dyDescent="0.4">
+      <c r="A21" s="43" t="s">
         <v>59</v>
       </c>
       <c r="B21" s="6"/>
@@ -1558,8 +1557,8 @@
       <c r="P21" s="20"/>
       <c r="Q21" s="2"/>
     </row>
-    <row r="22" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="45" t="s">
+    <row r="22" spans="1:17" ht="24" x14ac:dyDescent="0.4">
+      <c r="A22" s="43" t="s">
         <v>15</v>
       </c>
       <c r="B22" s="6"/>
@@ -1579,8 +1578,8 @@
       <c r="P22" s="20"/>
       <c r="Q22" s="2"/>
     </row>
-    <row r="23" spans="1:17" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="52" t="s">
+    <row r="23" spans="1:17" ht="24" x14ac:dyDescent="0.25">
+      <c r="A23" s="49" t="s">
         <v>60</v>
       </c>
       <c r="B23" s="6"/>
@@ -1639,39 +1638,39 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.453125" customWidth="1"/>
-    <col min="2" max="2" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="17" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.453125" customWidth="1"/>
+    <col min="1" max="1" width="36.42578125" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="17" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-    </row>
-    <row r="2" spans="1:20" ht="163" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="57"/>
+      <c r="P1" s="57"/>
+      <c r="Q1" s="57"/>
+      <c r="R1" s="57"/>
+      <c r="S1" s="57"/>
+      <c r="T1" s="57"/>
+    </row>
+    <row r="2" spans="1:20" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1727,8 +1726,8 @@
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:20" ht="25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="50" t="s">
+    <row r="3" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="47" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6"/>
@@ -1752,8 +1751,8 @@
       <c r="P3" s="26"/>
       <c r="Q3" s="3"/>
     </row>
-    <row r="4" spans="1:20" ht="25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="50" t="s">
+    <row r="4" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="47" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="6"/>
@@ -1779,8 +1778,8 @@
       <c r="P4" s="21"/>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5" spans="1:20" ht="25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="50" t="s">
+    <row r="5" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="47" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="6"/>
@@ -1804,8 +1803,8 @@
       </c>
       <c r="Q5" s="33"/>
     </row>
-    <row r="6" spans="1:20" ht="25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="51" t="s">
+    <row r="6" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="48" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="7"/>
@@ -1827,8 +1826,8 @@
       <c r="P6" s="26"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="1:20" ht="25" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="45" t="s">
+    <row r="7" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="43" t="s">
         <v>20</v>
       </c>
       <c r="B7" s="6"/>
@@ -1850,8 +1849,8 @@
       <c r="P7" s="30"/>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8" spans="1:20" ht="25" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="45" t="s">
+    <row r="8" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="43" t="s">
         <v>23</v>
       </c>
       <c r="B8" s="6"/>
@@ -1873,8 +1872,8 @@
       <c r="P8" s="20"/>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9" spans="1:20" ht="25" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="45" t="s">
+    <row r="9" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="43" t="s">
         <v>26</v>
       </c>
       <c r="B9" s="6"/>
@@ -1896,8 +1895,8 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="25" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="45" t="s">
+    <row r="10" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="43" t="s">
         <v>31</v>
       </c>
       <c r="B10" s="6"/>
@@ -1919,8 +1918,8 @@
       <c r="P10" s="20"/>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11" spans="1:20" ht="25" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="45" t="s">
+    <row r="11" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="43" t="s">
         <v>32</v>
       </c>
       <c r="B11" s="6"/>
@@ -1944,8 +1943,8 @@
       </c>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12" spans="1:20" ht="25" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="45" t="s">
+    <row r="12" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="43" t="s">
         <v>34</v>
       </c>
       <c r="B12" s="6"/>
@@ -1971,8 +1970,8 @@
       </c>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13" spans="1:20" ht="25" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="45" t="s">
+    <row r="13" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="43" t="s">
         <v>35</v>
       </c>
       <c r="B13" s="6"/>
@@ -1998,8 +1997,8 @@
       </c>
       <c r="Q13" s="2"/>
     </row>
-    <row r="14" spans="1:20" ht="25" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="45" t="s">
+    <row r="14" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="43" t="s">
         <v>65</v>
       </c>
       <c r="B14" s="6"/>
@@ -2023,8 +2022,8 @@
       <c r="P14" s="20"/>
       <c r="Q14" s="2"/>
     </row>
-    <row r="15" spans="1:20" ht="25" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="45" t="s">
+    <row r="15" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="43" t="s">
         <v>40</v>
       </c>
       <c r="B15" s="6"/>
@@ -2046,8 +2045,8 @@
       <c r="P15" s="20"/>
       <c r="Q15" s="2"/>
     </row>
-    <row r="16" spans="1:20" ht="25" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A16" s="45" t="s">
+    <row r="16" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="43" t="s">
         <v>50</v>
       </c>
       <c r="B16" s="6"/>
@@ -2069,8 +2068,8 @@
       <c r="P16" s="20"/>
       <c r="Q16" s="2"/>
     </row>
-    <row r="17" spans="1:17" ht="25" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A17" s="45" t="s">
+    <row r="17" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="43" t="s">
         <v>48</v>
       </c>
       <c r="B17" s="6"/>
@@ -2092,8 +2091,8 @@
       <c r="P17" s="20"/>
       <c r="Q17" s="2"/>
     </row>
-    <row r="18" spans="1:17" ht="25" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A18" s="45" t="s">
+    <row r="18" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="43" t="s">
         <v>51</v>
       </c>
       <c r="B18" s="6"/>
@@ -2115,8 +2114,8 @@
       <c r="P18" s="20"/>
       <c r="Q18" s="2"/>
     </row>
-    <row r="19" spans="1:17" ht="25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="52" t="s">
+    <row r="19" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="49" t="s">
         <v>53</v>
       </c>
       <c r="B19" s="6"/>
@@ -2138,8 +2137,8 @@
       <c r="P19" s="20"/>
       <c r="Q19" s="2"/>
     </row>
-    <row r="20" spans="1:17" ht="47.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A20" s="53" t="s">
+    <row r="20" spans="1:17" ht="48.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="50" t="s">
         <v>62</v>
       </c>
       <c r="B20" s="6"/>
@@ -2165,8 +2164,8 @@
       <c r="P20" s="20"/>
       <c r="Q20" s="2"/>
     </row>
-    <row r="21" spans="1:17" ht="25" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A21" s="45" t="s">
+    <row r="21" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="43" t="s">
         <v>59</v>
       </c>
       <c r="B21" s="6"/>
@@ -2188,14 +2187,13 @@
       <c r="P21" s="20"/>
       <c r="Q21" s="2"/>
     </row>
-    <row r="22" spans="1:17" ht="25" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="45" t="s">
+    <row r="22" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="43" t="s">
         <v>15</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="2"/>
       <c r="D22" s="14"/>
-      <c r="E22" s="46"/>
       <c r="F22" s="18"/>
       <c r="G22" s="2"/>
       <c r="H22" s="20"/>
@@ -2207,16 +2205,16 @@
       <c r="L22" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="M22" s="47"/>
-      <c r="N22" s="48"/>
+      <c r="M22" s="44"/>
+      <c r="N22" s="45"/>
       <c r="O22" s="2"/>
       <c r="P22" s="20"/>
       <c r="Q22" s="31" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="52" t="s">
+    <row r="23" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="49" t="s">
         <v>60</v>
       </c>
       <c r="B23" s="6"/>
@@ -2276,222 +2274,222 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3352D7AE-DE03-4C47-9317-E12938A32132}">
   <dimension ref="A2:C24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.81640625" customWidth="1"/>
-    <col min="2" max="2" width="62.453125" customWidth="1"/>
-    <col min="3" max="3" width="26.7265625" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="62.42578125" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="49" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="46" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="51" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="51" t="s">
         <v>4</v>
       </c>
       <c r="C4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="51" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="55" t="s">
+      <c r="B6" s="52" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="52" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="51" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="51" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="54" t="s">
+      <c r="B10" s="51" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="54" t="s">
+      <c r="B11" s="51" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:3" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="56" t="s">
+      <c r="B12" s="53" t="s">
         <v>71</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:3" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="55" t="s">
+      <c r="B13" s="52" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="54" t="s">
         <v>36</v>
       </c>
       <c r="C14" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="57" t="s">
+      <c r="B15" s="54" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="57" t="s">
+      <c r="B16" s="54" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="57" t="s">
+      <c r="B17" s="54" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="58" t="s">
+      <c r="B18" s="55" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="58" t="s">
+      <c r="B19" s="55" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="58" t="s">
+      <c r="B20" s="55" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="58" t="s">
+      <c r="B21" s="55" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="57" t="s">
+      <c r="B22" s="54" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="58" t="s">
+      <c r="B23" s="55" t="s">
         <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="58" t="s">
+      <c r="B24" s="55" t="s">
         <v>74</v>
       </c>
     </row>
